--- a/AutoHotkey/キー配列.xlsx
+++ b/AutoHotkey/キー配列.xlsx
@@ -5,11 +5,10 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet1_2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="103">
   <si>
     <t xml:space="preserve">通常（US配列）</t>
   </si>
@@ -116,7 +115,7 @@
     <t xml:space="preserve">'</t>
   </si>
   <si>
-    <t xml:space="preserve">Enter</t>
+    <t xml:space="preserve">⏎</t>
   </si>
   <si>
     <t xml:space="preserve">Shift</t>
@@ -149,139 +148,148 @@
     <t xml:space="preserve">.</t>
   </si>
   <si>
+    <t xml:space="preserve">/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ctrl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Win</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space押下レイヤー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">戻る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">進む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhlUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">半/全</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VolDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VolUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">^</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WhlDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_</t>
+  </si>
+  <si>
     <t xml:space="preserve">?</t>
   </si>
   <si>
-    <t xml:space="preserve">Ctrl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Win</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">App</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space押下レイヤー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">戻る</t>
-  </si>
-  <si>
-    <t xml:space="preserve">進む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhlUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¥</t>
-  </si>
-  <si>
-    <t xml:space="preserve">半/全</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">↑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VolDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VolUP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">^</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">→</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WhlDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_</t>
-  </si>
-  <si>
     <t xml:space="preserve">@</t>
   </si>
   <si>
-    <t xml:space="preserve">Delete</t>
+    <t xml:space="preserve">DEL</t>
   </si>
   <si>
     <t xml:space="preserve">無変換</t>
@@ -296,46 +304,31 @@
     <t xml:space="preserve">変換</t>
   </si>
   <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　</t>
+  </si>
+  <si>
     <t xml:space="preserve">Space＋Shift押下レイヤー</t>
   </si>
   <si>
     <t xml:space="preserve">$</t>
   </si>
   <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(</t>
-  </si>
-  <si>
-    <t xml:space="preserve">)</t>
-  </si>
-  <si>
     <t xml:space="preserve">#</t>
   </si>
   <si>
-    <t xml:space="preserve">:</t>
-  </si>
-  <si>
     <t xml:space="preserve">{</t>
   </si>
   <si>
     <t xml:space="preserve">}</t>
   </si>
   <si>
-    <t xml:space="preserve">!</t>
-  </si>
-  <si>
     <t xml:space="preserve">“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⏎</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　</t>
   </si>
 </sst>
 </file>
@@ -474,7 +467,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -495,7 +488,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -523,28 +516,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -559,8 +536,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -746,845 +731,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C2:S23"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="22.05" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="9.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="4.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="3" width="4.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="1.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="12" style="3" width="4.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="20" style="1" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="2" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="2"/>
-      <c r="D2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-    </row>
-    <row r="3" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="2"/>
-      <c r="D3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M3" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N3" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="O3" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="2"/>
-      <c r="D4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="2"/>
-      <c r="D5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" s="7"/>
-    </row>
-    <row r="6" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="2"/>
-      <c r="D6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-    </row>
-    <row r="7" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="2"/>
-      <c r="D7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-    </row>
-    <row r="11" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="2"/>
-      <c r="D11" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="P11" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="S11" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="2"/>
-      <c r="D12" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="P12" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="R12" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="S12" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="2"/>
-      <c r="D13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R13" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="S13" s="13"/>
-    </row>
-    <row r="14" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="2"/>
-      <c r="D14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-    </row>
-    <row r="15" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="2"/>
-      <c r="D15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-    </row>
-    <row r="19" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C19" s="2"/>
-      <c r="D19" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="M19" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="N19" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="P19" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q19" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="S19" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C20" s="2"/>
-      <c r="D20" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="N20" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="O20" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="P20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q20" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="R20" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="S20" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C21" s="2"/>
-      <c r="D21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="K21" s="6"/>
-      <c r="L21" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="M21" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="N21" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="O21" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="P21" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="R21" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="S21" s="13"/>
-    </row>
-    <row r="22" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="2"/>
-      <c r="D22" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-    </row>
-    <row r="23" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="2"/>
-      <c r="D23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="D2:S2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="R5:S5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="G7:N7"/>
-    <mergeCell ref="D10:S10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="G15:N15"/>
-    <mergeCell ref="D18:S18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="G23:N23"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="C2:AK23"/>
+  <dimension ref="C2:AK27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="22.05" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
@@ -1604,43 +751,43 @@
   <sheetData>
     <row r="2" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="2"/>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
       <c r="U2" s="2"/>
-      <c r="V2" s="16" t="s">
+      <c r="V2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-      <c r="AE2" s="16"/>
-      <c r="AF2" s="16"/>
-      <c r="AG2" s="16"/>
-      <c r="AH2" s="16"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="16"/>
-      <c r="AK2" s="16"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="5"/>
+      <c r="AF2" s="5"/>
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="5"/>
+      <c r="AI2" s="5"/>
+      <c r="AJ2" s="5"/>
+      <c r="AK2" s="5"/>
     </row>
     <row r="3" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="2"/>
@@ -1867,7 +1014,7 @@
         <v>30</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="S5" s="7"/>
       <c r="U5" s="2"/>
@@ -1910,7 +1057,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" s="7" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="AK5" s="7"/>
     </row>
@@ -1949,7 +1096,7 @@
         <v>41</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>32</v>
@@ -1990,7 +1137,7 @@
         <v>41</v>
       </c>
       <c r="AH6" s="6" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>32</v>
@@ -2135,42 +1282,42 @@
       <c r="AK9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="V10" s="17" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="V10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="W10" s="17"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="17"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="17"/>
-      <c r="AC10" s="17"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="17"/>
-      <c r="AF10" s="17"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="17"/>
-      <c r="AI10" s="17"/>
-      <c r="AJ10" s="17"/>
-      <c r="AK10" s="17"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="12"/>
+      <c r="AB10" s="12"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="12"/>
+      <c r="AE10" s="12"/>
+      <c r="AF10" s="12"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="12"/>
+      <c r="AI10" s="12"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
     </row>
     <row r="11" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="2"/>
@@ -2277,35 +1424,35 @@
         <v>66</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>18</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="N12" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="O12" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="O12" s="13" t="s">
-        <v>72</v>
       </c>
       <c r="P12" s="13" t="s">
         <v>4</v>
       </c>
       <c r="Q12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="R12" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="R12" s="13" t="s">
-        <v>74</v>
       </c>
       <c r="S12" s="7"/>
       <c r="U12" s="2"/>
@@ -2320,35 +1467,35 @@
         <v>66</v>
       </c>
       <c r="Z12" s="13" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="AA12" s="13" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="AB12" s="13" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AC12" s="6"/>
       <c r="AD12" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE12" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AE12" s="13" t="s">
+      <c r="AF12" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AF12" s="13" t="s">
+      <c r="AG12" s="13" t="s">
         <v>71</v>
-      </c>
-      <c r="AG12" s="13" t="s">
-        <v>72</v>
       </c>
       <c r="AH12" s="13" t="s">
         <v>4</v>
       </c>
       <c r="AI12" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ12" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="AJ12" s="13" t="s">
-        <v>74</v>
       </c>
       <c r="AK12" s="7"/>
     </row>
@@ -2357,52 +1504,52 @@
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>2</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="s">
         <v>1</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13" s="18" t="s">
-        <v>102</v>
+        <v>83</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="S13" s="13"/>
       <c r="U13" s="2"/>
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Y13" s="13" t="s">
         <v>2</v>
       </c>
       <c r="Z13" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA13" s="13" t="s">
         <v>16</v>
@@ -2415,20 +1562,20 @@
         <v>1</v>
       </c>
       <c r="AE13" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AF13" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AG13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH13" s="18" t="s">
-        <v>102</v>
+        <v>83</v>
+      </c>
+      <c r="AH13" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="AI13" s="7"/>
       <c r="AJ13" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AK13" s="13"/>
     </row>
@@ -2440,32 +1587,32 @@
         <v>3</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="O14" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="P14" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -2477,32 +1624,32 @@
         <v>3</v>
       </c>
       <c r="Y14" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Z14" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AA14" s="13" t="s">
         <v>30</v>
       </c>
       <c r="AB14" s="13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AC14" s="6"/>
       <c r="AD14" s="13" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="AE14" s="13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AF14" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AG14" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AH14" s="13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AI14" s="7"/>
       <c r="AJ14" s="7"/>
@@ -2514,7 +1661,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="8" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
@@ -2533,7 +1680,7 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="8" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
@@ -2617,42 +1764,42 @@
       <c r="AK17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="17.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="V18" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="19"/>
-      <c r="AC18" s="19"/>
-      <c r="AD18" s="19"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="19"/>
-      <c r="AG18" s="19"/>
-      <c r="AH18" s="19"/>
-      <c r="AI18" s="19"/>
-      <c r="AJ18" s="19"/>
-      <c r="AK18" s="19"/>
+      <c r="D18" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="V18" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15"/>
+      <c r="AB18" s="15"/>
+      <c r="AC18" s="15"/>
+      <c r="AD18" s="15"/>
+      <c r="AE18" s="15"/>
+      <c r="AF18" s="15"/>
+      <c r="AG18" s="15"/>
+      <c r="AH18" s="15"/>
+      <c r="AI18" s="15"/>
+      <c r="AJ18" s="15"/>
+      <c r="AK18" s="15"/>
     </row>
     <row r="19" s="4" customFormat="true" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="2"/>
@@ -2662,7 +1809,7 @@
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="20"/>
+      <c r="J19" s="16"/>
       <c r="K19" s="6"/>
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
@@ -2679,7 +1826,7 @@
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
       <c r="AA19" s="7"/>
-      <c r="AB19" s="20"/>
+      <c r="AB19" s="16"/>
       <c r="AC19" s="6"/>
       <c r="AD19" s="7"/>
       <c r="AE19" s="7"/>
@@ -2694,20 +1841,20 @@
       <c r="C20" s="2"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="H20" s="15" t="s">
+      <c r="F20" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="I20" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>96</v>
+      <c r="H20" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="7"/>
@@ -2721,20 +1868,20 @@
       <c r="U20" s="2"/>
       <c r="V20" s="7"/>
       <c r="W20" s="7"/>
-      <c r="X20" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y20" s="15" t="s">
+      <c r="X20" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y20" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="Z20" s="21" t="s">
+      <c r="Z20" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA20" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="AA20" s="21" t="s">
+      <c r="AB20" s="17" t="s">
         <v>67</v>
-      </c>
-      <c r="AB20" s="15" t="s">
-        <v>68</v>
       </c>
       <c r="AC20" s="6"/>
       <c r="AD20" s="7"/>
@@ -2750,20 +1897,20 @@
       <c r="C21" s="2"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="15" t="s">
+      <c r="F21" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="J21" s="15" t="s">
+      <c r="H21" s="17" t="s">
         <v>100</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="7"/>
@@ -2777,20 +1924,20 @@
       <c r="U21" s="2"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7"/>
-      <c r="X21" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y21" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z21" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA21" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB21" s="15" t="s">
+      <c r="X21" s="17" t="s">
         <v>99</v>
+      </c>
+      <c r="Y21" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z21" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA21" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB21" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="AC21" s="6"/>
       <c r="AD21" s="7"/>
@@ -2806,16 +1953,16 @@
       <c r="C22" s="2"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" s="15" t="s">
+      <c r="G22" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H22" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="17" t="s">
         <v>17</v>
       </c>
       <c r="J22" s="7"/>
@@ -2831,17 +1978,17 @@
       <c r="U22" s="2"/>
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
-      <c r="X22" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y22" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z22" s="21" t="s">
+      <c r="X22" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z22" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="AA22" s="15" t="s">
-        <v>101</v>
+      <c r="AA22" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="AB22" s="7"/>
       <c r="AC22" s="6"/>
@@ -2889,6 +2036,9 @@
       <c r="AI23" s="7"/>
       <c r="AJ23" s="7"/>
       <c r="AK23" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W27" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -2943,7 +2093,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>

--- a/AutoHotkey/キー配列.xlsx
+++ b/AutoHotkey/キー配列.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="119">
   <si>
     <r>
       <rPr>
@@ -363,212 +363,8 @@
     <t xml:space="preserve">　</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cascadia Code"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Space</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cascadia Mono"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cascadia Code"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Alt+Win+Ctrl</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">押下レイヤー</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">NumLock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(</t>
-  </si>
-  <si>
-    <t xml:space="preserve">)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num⏎</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asdf</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cascadia Code"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cascadia Mono"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">セミコロン</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cascadia Code"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Cascadia Mono"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">押下レイヤー</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">
-`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-&amp;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-|</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
--</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">^</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{</t>
-  </si>
-  <si>
-    <t xml:space="preserve">}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;</t>
+    <t xml:space="preserve">”
+’</t>
   </si>
   <si>
     <t xml:space="preserve">@
@@ -579,11 +375,11 @@
 =</t>
   </si>
   <si>
-    <t xml:space="preserve">'
+    <t xml:space="preserve">{
 (</t>
   </si>
   <si>
-    <t xml:space="preserve">“
+    <t xml:space="preserve">}
 )</t>
   </si>
   <si>
@@ -614,6 +410,79 @@
   </si>
   <si>
     <t xml:space="preserve">PgDn</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cascadia Code"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Alt+Win+Ctrl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">押下レイヤー</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NumLock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num⏎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num0</t>
   </si>
 </sst>
 </file>
@@ -681,6 +550,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Cascadia Code"/>
       <family val="2"/>
       <charset val="1"/>
@@ -692,15 +568,8 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Cascadia Mono"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -731,6 +600,12 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFF9900"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -773,7 +648,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -862,16 +737,28 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -928,7 +815,7 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF81D41A"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
@@ -1123,7 +1010,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD39"/>
+  <dimension ref="A1:XFD1048576"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="34" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="10.53"/>
@@ -1514,6 +1401,9 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
+      <c r="U8" s="1" t="n">
+        <v>456</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D9" s="7"/>
@@ -1532,6 +1422,9 @@
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
+      <c r="U9" s="1" t="n">
+        <v>4564.456</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -1876,341 +1769,275 @@
       <c r="S16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D18" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D19" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K19" s="9"/>
+      <c r="L19" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="O19" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="P19" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D20" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="22"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="5"/>
-      <c r="AA17" s="5"/>
-      <c r="AB17" s="5"/>
-      <c r="AC17" s="5"/>
-      <c r="AD17" s="5"/>
-      <c r="AE17" s="5"/>
-      <c r="AF17" s="5"/>
-      <c r="AG17" s="5"/>
-      <c r="AH17" s="5"/>
-      <c r="AI17" s="5"/>
-      <c r="AJ17" s="5"/>
-      <c r="AK17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C18" s="7"/>
-      <c r="D18" s="17" t="s">
+      <c r="E20" s="23"/>
+      <c r="F20" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="20" t="s">
         <v>94</v>
-      </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="M18" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="N18" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="O18" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
-      <c r="Z18" s="5"/>
-      <c r="AA18" s="5"/>
-      <c r="AB18" s="5"/>
-      <c r="AC18" s="5"/>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="5"/>
-      <c r="AF18" s="5"/>
-      <c r="AG18" s="5"/>
-      <c r="AH18" s="5"/>
-      <c r="AI18" s="5"/>
-      <c r="AJ18" s="5"/>
-      <c r="AK18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="7"/>
-      <c r="D19" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="N19" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="O19" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="P19" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q19" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="R19" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="S19" s="11"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="4"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
-      <c r="AA19" s="5"/>
-      <c r="AB19" s="5"/>
-      <c r="AC19" s="5"/>
-      <c r="AD19" s="5"/>
-      <c r="AE19" s="5"/>
-      <c r="AF19" s="5"/>
-      <c r="AG19" s="5"/>
-      <c r="AH19" s="5"/>
-      <c r="AI19" s="5"/>
-      <c r="AJ19" s="5"/>
-      <c r="AK19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C20" s="7"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>101</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>102</v>
+        <v>1</v>
+      </c>
+      <c r="M20" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="N20" s="18" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="O20" s="18" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="P20" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="S20" s="17"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5" t="n">
-        <v>466</v>
-      </c>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="5"/>
-      <c r="AA20" s="5"/>
-      <c r="AB20" s="5"/>
-      <c r="AC20" s="5"/>
-      <c r="AD20" s="5"/>
-      <c r="AE20" s="5"/>
-      <c r="AF20" s="5"/>
-      <c r="AG20" s="5"/>
-      <c r="AH20" s="5"/>
-      <c r="AI20" s="5"/>
-      <c r="AJ20" s="5"/>
-      <c r="AK20" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="Q20" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="R20" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="S20" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="XFD20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="18" t="s">
-        <v>106</v>
+      <c r="F21" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="K21" s="9"/>
-      <c r="L21" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="M21" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="N21" s="21" t="s">
-        <v>109</v>
+      <c r="L21" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="M21" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="N21" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="O21" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="P21" s="20" t="s">
-        <v>41</v>
+        <v>81</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
-      <c r="S21" s="11"/>
-      <c r="T21" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="U21" s="5" t="n">
-        <v>478912</v>
-      </c>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="5"/>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5"/>
-      <c r="AF21" s="5"/>
-      <c r="AG21" s="5"/>
-      <c r="AH21" s="5"/>
-      <c r="AI21" s="5"/>
-      <c r="AJ21" s="5"/>
-      <c r="AK21" s="5"/>
+      <c r="R21" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="S21" s="17"/>
     </row>
     <row r="22" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
+      <c r="F22" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="K22" s="9"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="O22" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="P22" s="18"/>
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
       <c r="S22" s="11"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5"/>
-      <c r="AF22" s="5"/>
-      <c r="AG22" s="5"/>
-      <c r="AH22" s="5"/>
-      <c r="AI22" s="5"/>
-      <c r="AJ22" s="5"/>
-      <c r="AK22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-    </row>
-    <row r="24" s="4" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" s="4" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D25" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-    </row>
-    <row r="26" s="4" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="11"/>
+      <c r="R23" s="11"/>
+      <c r="S23" s="11"/>
+    </row>
+    <row r="24" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D24" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
+    </row>
+    <row r="25" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D25" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="N25" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="O25" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D26" s="17" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="E26" s="17"/>
       <c r="F26" s="18"/>
@@ -2219,358 +2046,121 @@
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
       <c r="K26" s="9"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="19"/>
-    </row>
-    <row r="27" s="4" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D27" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>118</v>
-      </c>
+      <c r="L26" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="M26" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="N26" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="O26" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="R26" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="S26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="21"/>
       <c r="K27" s="9"/>
       <c r="L27" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="M27" s="21" t="s">
-        <v>98</v>
+        <v>112</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="O27" s="18" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="P27" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="11"/>
-    </row>
-    <row r="28" s="4" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>115</v>
+      </c>
+      <c r="Q27" s="11"/>
+      <c r="R27" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="S27" s="17"/>
+    </row>
+    <row r="28" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
-      <c r="F28" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="I28" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>18</v>
-      </c>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="20"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="M28" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="N28" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="O28" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="P28" s="13" t="s">
-        <v>29</v>
-      </c>
+      <c r="L28" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="M28" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="N28" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="O28" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="P28" s="20"/>
       <c r="Q28" s="11"/>
-      <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-    </row>
-    <row r="29" s="4" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="R28" s="11"/>
+      <c r="S28" s="11"/>
+    </row>
+    <row r="29" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
-      <c r="F29" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="I29" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="J29" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="M29" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="N29" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="O29" s="18"/>
-      <c r="P29" s="18" t="s">
-        <v>133</v>
-      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
       <c r="S29" s="11"/>
     </row>
-    <row r="30" s="4" customFormat="true" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="11"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D32" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-    </row>
-    <row r="33" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D33" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="M33" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="N33" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="O33" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="P33" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D34" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="J34" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="M34" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="N34" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="O34" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="P34" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q34" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="R34" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="S34" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="XFD34" s="0"/>
-    </row>
-    <row r="35" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I35" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="K35" s="9"/>
-      <c r="L35" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="M35" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="N35" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="O35" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="P35" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="S35" s="17"/>
-    </row>
-    <row r="36" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="G36" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="I36" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="J36" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="K36" s="9"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="O36" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
-      <c r="S36" s="11"/>
-    </row>
-    <row r="37" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="11"/>
-    </row>
-    <row r="39" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F39" s="0"/>
-      <c r="G39" s="0"/>
-      <c r="H39" s="0"/>
-      <c r="J39" s="0"/>
-    </row>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="32">
     <mergeCell ref="D2:S2"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="D4:E4"/>
@@ -2587,30 +2177,22 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="Q14:S14"/>
     <mergeCell ref="G15:N15"/>
-    <mergeCell ref="D17:S17"/>
-    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D18:S18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="R20:S20"/>
     <mergeCell ref="D21:E21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="G22:N22"/>
-    <mergeCell ref="D25:S25"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="G23:N23"/>
+    <mergeCell ref="D24:S24"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="D27:E27"/>
+    <mergeCell ref="R27:S27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="G30:N30"/>
-    <mergeCell ref="D32:S32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="G37:N37"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="G29:N29"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/AutoHotkey/キー配列.xlsx
+++ b/AutoHotkey/キー配列.xlsx
@@ -1586,8 +1586,8 @@
         <v>78</v>
       </c>
       <c r="K12" s="10"/>
-      <c r="L12" s="20" t="s">
-        <v>1</v>
+      <c r="L12" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="M12" s="20" t="s">
         <v>79</v>
